--- a/2026/Biodata MABAIZ.xlsx
+++ b/2026/Biodata MABAIZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\wisuda-2025\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD69438-7074-41BF-BD7D-2F7A9A1B5807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817FD245-0A97-4792-A603-FFB7D52C2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{6E6CECD0-E5C0-4D5E-92DD-07FA2212974F}"/>
   </bookViews>

--- a/2026/Biodata MABAIZ.xlsx
+++ b/2026/Biodata MABAIZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\wisuda-2025\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817FD245-0A97-4792-A603-FFB7D52C2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B88B37-0375-4D1D-8692-580379DD07EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{6E6CECD0-E5C0-4D5E-92DD-07FA2212974F}"/>
   </bookViews>

--- a/2026/Biodata MABAIZ.xlsx
+++ b/2026/Biodata MABAIZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\wisuda-2025\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B88B37-0375-4D1D-8692-580379DD07EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A755A389-D3F3-4BC2-9B6B-4A5CFCBE8323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" xr2:uid="{6E6CECD0-E5C0-4D5E-92DD-07FA2212974F}"/>
   </bookViews>
